--- a/Local_Refinement_Results.xlsx
+++ b/Local_Refinement_Results.xlsx
@@ -253,74 +253,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BM6"/>
+  <dimension ref="A1:BM11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.85546875" customWidth="true"/>
-    <col min="2" max="2" width="16.42578125" customWidth="true"/>
+    <col min="2" max="2" width="16.28515625" customWidth="true"/>
     <col min="3" max="3" width="10.28515625" customWidth="true"/>
-    <col min="4" max="4" width="15.5703125" customWidth="true"/>
-    <col min="5" max="5" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true"/>
+    <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="14.7109375" customWidth="true"/>
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="3.140625" customWidth="true"/>
     <col min="9" max="9" width="14.7109375" customWidth="true"/>
     <col min="10" max="10" width="14.7109375" customWidth="true"/>
-    <col min="11" max="11" width="12.7109375" customWidth="true"/>
+    <col min="11" max="11" width="3.140625" customWidth="true"/>
     <col min="12" max="12" width="14.7109375" customWidth="true"/>
     <col min="13" max="13" width="14.7109375" customWidth="true"/>
-    <col min="14" max="14" width="12.7109375" customWidth="true"/>
+    <col min="14" max="14" width="3.140625" customWidth="true"/>
     <col min="15" max="15" width="14.7109375" customWidth="true"/>
     <col min="16" max="16" width="14.7109375" customWidth="true"/>
-    <col min="17" max="17" width="13.7109375" customWidth="true"/>
+    <col min="17" max="17" width="4.140625" customWidth="true"/>
     <col min="18" max="18" width="14.7109375" customWidth="true"/>
     <col min="19" max="19" width="14.7109375" customWidth="true"/>
-    <col min="20" max="20" width="12.7109375" customWidth="true"/>
+    <col min="20" max="20" width="4.140625" customWidth="true"/>
     <col min="21" max="21" width="14.7109375" customWidth="true"/>
     <col min="22" max="22" width="14.7109375" customWidth="true"/>
-    <col min="23" max="23" width="12.7109375" customWidth="true"/>
+    <col min="23" max="23" width="4.140625" customWidth="true"/>
     <col min="24" max="24" width="14.7109375" customWidth="true"/>
     <col min="25" max="25" width="14.7109375" customWidth="true"/>
-    <col min="26" max="26" width="12.7109375" customWidth="true"/>
+    <col min="26" max="26" width="4.140625" customWidth="true"/>
     <col min="27" max="27" width="14.7109375" customWidth="true"/>
     <col min="28" max="28" width="14.7109375" customWidth="true"/>
-    <col min="29" max="29" width="12.7109375" customWidth="true"/>
+    <col min="29" max="29" width="4.140625" customWidth="true"/>
     <col min="30" max="30" width="14.7109375" customWidth="true"/>
     <col min="31" max="31" width="14.7109375" customWidth="true"/>
-    <col min="32" max="32" width="12.7109375" customWidth="true"/>
+    <col min="32" max="32" width="4.140625" customWidth="true"/>
     <col min="33" max="33" width="14.7109375" customWidth="true"/>
     <col min="34" max="34" width="14.7109375" customWidth="true"/>
-    <col min="35" max="35" width="11.7109375" customWidth="true"/>
+    <col min="35" max="35" width="4.140625" customWidth="true"/>
     <col min="36" max="36" width="14.7109375" customWidth="true"/>
     <col min="37" max="37" width="14.7109375" customWidth="true"/>
-    <col min="38" max="38" width="12.7109375" customWidth="true"/>
+    <col min="38" max="38" width="4.140625" customWidth="true"/>
     <col min="39" max="39" width="14.7109375" customWidth="true"/>
     <col min="40" max="40" width="14.7109375" customWidth="true"/>
-    <col min="41" max="41" width="12.7109375" customWidth="true"/>
+    <col min="41" max="41" width="4.140625" customWidth="true"/>
     <col min="42" max="42" width="14.7109375" customWidth="true"/>
     <col min="43" max="43" width="14.7109375" customWidth="true"/>
-    <col min="44" max="44" width="12.7109375" customWidth="true"/>
+    <col min="44" max="44" width="4.140625" customWidth="true"/>
     <col min="45" max="45" width="14.7109375" customWidth="true"/>
     <col min="46" max="46" width="14.7109375" customWidth="true"/>
-    <col min="47" max="47" width="12.7109375" customWidth="true"/>
+    <col min="47" max="47" width="4.140625" customWidth="true"/>
     <col min="48" max="48" width="14.7109375" customWidth="true"/>
     <col min="49" max="49" width="14.7109375" customWidth="true"/>
-    <col min="50" max="50" width="12.7109375" customWidth="true"/>
+    <col min="50" max="50" width="4.140625" customWidth="true"/>
     <col min="51" max="51" width="14.7109375" customWidth="true"/>
     <col min="52" max="52" width="14.7109375" customWidth="true"/>
-    <col min="53" max="53" width="12.7109375" customWidth="true"/>
+    <col min="53" max="53" width="4.140625" customWidth="true"/>
     <col min="54" max="54" width="14.7109375" customWidth="true"/>
     <col min="55" max="55" width="14.7109375" customWidth="true"/>
-    <col min="56" max="56" width="12.7109375" customWidth="true"/>
+    <col min="56" max="56" width="4.140625" customWidth="true"/>
     <col min="57" max="57" width="14.7109375" customWidth="true"/>
     <col min="58" max="58" width="14.7109375" customWidth="true"/>
-    <col min="59" max="59" width="12.7109375" customWidth="true"/>
+    <col min="59" max="59" width="4.140625" customWidth="true"/>
     <col min="60" max="60" width="14.7109375" customWidth="true"/>
     <col min="61" max="61" width="14.7109375" customWidth="true"/>
-    <col min="62" max="62" width="11.7109375" customWidth="true"/>
+    <col min="62" max="62" width="4.140625" customWidth="true"/>
     <col min="63" max="63" width="14.7109375" customWidth="true"/>
     <col min="64" max="64" width="14.7109375" customWidth="true"/>
-    <col min="65" max="65" width="11.7109375" customWidth="true"/>
+    <col min="65" max="65" width="4.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,7 +525,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="0">
-        <v>-0.00060667761096454829</v>
+        <v>-1.9195755897873019e-08</v>
       </c>
       <c r="C2" s="0">
         <v>0</v>
@@ -534,187 +534,187 @@
         <v>0</v>
       </c>
       <c r="E2" s="0">
-        <v>0.23447196040901222</v>
+        <v>2.1849421572659963e-05</v>
       </c>
       <c r="F2" s="0">
-        <v>0.0043211949999999999</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="G2" s="0">
-        <v>0.0058275949999999997</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="H2" s="0">
         <v>0</v>
       </c>
       <c r="I2" s="0">
-        <v>0.0033933740000000002</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="J2" s="0">
-        <v>0.0047553880000000001</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="K2" s="0">
-        <v>0.42577978100000002</v>
+        <v>0</v>
       </c>
       <c r="L2" s="0">
-        <v>0.0048090340000000002</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="M2" s="0">
-        <v>0.0045822409999999999</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="N2" s="0">
-        <v>0.439620542</v>
+        <v>0</v>
       </c>
       <c r="O2" s="0">
-        <v>0.0043288709999999998</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="P2" s="0">
-        <v>0.0013724080000000001</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.021058184000000001</v>
+        <v>0</v>
       </c>
       <c r="R2" s="0">
-        <v>0.0059108800000000003</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="S2" s="0">
-        <v>0.0056127649999999996</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="T2" s="0">
-        <v>0.63397581000000003</v>
+        <v>0</v>
       </c>
       <c r="U2" s="0">
-        <v>0.002437818</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="V2" s="0">
-        <v>0.0054762830000000002</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="W2" s="0">
-        <v>0.38236099000000001</v>
+        <v>0</v>
       </c>
       <c r="X2" s="0">
-        <v>0.0040549280000000002</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.001445563</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.21064950499999999</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.00170973</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.0020899870000000002</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AC2" s="0">
-        <v>0.37013944999999998</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.0017267389999999999</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AE2" s="0">
-        <v>0.0020974349999999999</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.102848983</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.001240948</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.0039091500000000001</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AI2" s="0">
-        <v>1.365199871</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.001725348</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AK2" s="0">
-        <v>0.001866223</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AL2" s="0">
-        <v>0.83667712699999996</v>
+        <v>0</v>
       </c>
       <c r="AM2" s="0">
-        <v>0.0017246220000000001</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AN2" s="0">
-        <v>0.00176954</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AO2" s="0">
-        <v>0.26512952000000001</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="0">
-        <v>0.0024635680000000002</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AQ2" s="0">
-        <v>0.0013515420000000001</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AR2" s="0">
-        <v>0.375414947</v>
+        <v>0</v>
       </c>
       <c r="AS2" s="0">
-        <v>0.002498896</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AT2" s="0">
-        <v>0.0012756320000000001</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AU2" s="0">
-        <v>0.985984478</v>
+        <v>0</v>
       </c>
       <c r="AV2" s="0">
-        <v>0.0021053410000000002</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AW2" s="0">
-        <v>0.0012723949999999999</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AX2" s="0">
-        <v>0.52290469799999995</v>
+        <v>0</v>
       </c>
       <c r="AY2" s="0">
-        <v>0.0031840760000000001</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="AZ2" s="0">
-        <v>0.0023940189999999998</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="BA2" s="0">
-        <v>0.15824516</v>
+        <v>0</v>
       </c>
       <c r="BB2" s="0">
-        <v>0.0044510749999999996</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="BC2" s="0">
-        <v>0.0051600320000000002</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="BD2" s="0">
-        <v>0.48272798900000002</v>
+        <v>0</v>
       </c>
       <c r="BE2" s="0">
-        <v>0.0054703470000000004</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="BF2" s="0">
-        <v>0.005003258</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="BG2" s="0">
-        <v>0.87095528300000002</v>
+        <v>0</v>
       </c>
       <c r="BH2" s="0">
-        <v>0.0055471490000000004</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="BI2" s="0">
-        <v>0.0057562960000000002</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="BJ2" s="0">
-        <v>1.126630507</v>
+        <v>0</v>
       </c>
       <c r="BK2" s="0">
-        <v>0.0054834619999999997</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="BL2" s="0">
-        <v>0.0052185879999999997</v>
+        <v>0.0035115649158406724</v>
       </c>
       <c r="BM2" s="0">
-        <v>1.1509312389999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -722,196 +722,196 @@
         <v>1</v>
       </c>
       <c r="B3" s="0">
-        <v>-0.00060899663533045046</v>
+        <v>-1.9680773322522634e-08</v>
       </c>
       <c r="C3" s="0">
         <v>0</v>
       </c>
       <c r="D3" s="0">
-        <v>1.2798342154537886e-05</v>
+        <v>2.1849421572660028e-05</v>
       </c>
       <c r="E3" s="0">
-        <v>0.23317541234766073</v>
+        <v>2.2540097564044094e-05</v>
       </c>
       <c r="F3" s="0">
-        <v>0.0043213456045263967</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="G3" s="0">
-        <v>0.0058276822104568402</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="H3" s="0">
         <v>0</v>
       </c>
       <c r="I3" s="0">
-        <v>0.0033933175635545896</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="J3" s="0">
-        <v>0.0047554934146417111</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="K3" s="0">
-        <v>0.42577978106991138</v>
+        <v>0</v>
       </c>
       <c r="L3" s="0">
-        <v>0.0048093622536276243</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="M3" s="0">
-        <v>0.0045828370354730119</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="N3" s="0">
-        <v>0.43962054199933998</v>
+        <v>0</v>
       </c>
       <c r="O3" s="0">
-        <v>0.0043304197640377995</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="P3" s="0">
-        <v>0.0013715416653554706</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.021058084300960032</v>
+        <v>0</v>
       </c>
       <c r="R3" s="0">
-        <v>0.0059110873203140658</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="S3" s="0">
-        <v>0.0056136658267708379</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="T3" s="0">
-        <v>0.63397581022107796</v>
+        <v>0</v>
       </c>
       <c r="U3" s="0">
-        <v>0.0024461047222957598</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="V3" s="0">
-        <v>0.0054775013255489386</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="W3" s="0">
-        <v>0.3823610211322474</v>
+        <v>0</v>
       </c>
       <c r="X3" s="0">
-        <v>0.0040569698756500903</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.0014445264845029632</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.21064937243808832</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="0">
-        <v>0.0017080789514530787</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.0020874513576395063</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.37013946842669393</v>
+        <v>0</v>
       </c>
       <c r="AD3" s="0">
-        <v>0.0017250483833289544</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.0020948820313188244</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.10284903573425425</v>
+        <v>0</v>
       </c>
       <c r="AG3" s="0">
-        <v>0.0012403886491765697</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AH3" s="0">
-        <v>0.0039107615557272216</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AI3" s="0">
-        <v>1.3651996491762686</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.0017236606192194042</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AK3" s="0">
-        <v>0.0018642079009828245</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AL3" s="0">
-        <v>0.83667713162607693</v>
+        <v>0</v>
       </c>
       <c r="AM3" s="0">
-        <v>0.0017229363081169356</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AN3" s="0">
-        <v>0.0017677498151426629</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AO3" s="0">
-        <v>0.26512952610499485</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="0">
-        <v>0.0024601632942390481</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AQ3" s="0">
-        <v>0.0013507242060385191</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AR3" s="0">
-        <v>0.37541498066771373</v>
+        <v>0</v>
       </c>
       <c r="AS3" s="0">
-        <v>0.0024954091105310662</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AT3" s="0">
-        <v>0.0012749907958616868</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AU3" s="0">
-        <v>0.98598461456782849</v>
+        <v>0</v>
       </c>
       <c r="AV3" s="0">
-        <v>0.0021027696395503888</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AW3" s="0">
-        <v>0.0012717613261114245</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AX3" s="0">
-        <v>0.5229048169562075</v>
+        <v>0</v>
       </c>
       <c r="AY3" s="0">
-        <v>0.0031799558011257876</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="AZ3" s="0">
-        <v>0.0023936838865285187</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="BA3" s="0">
-        <v>0.15824516801868962</v>
+        <v>0</v>
       </c>
       <c r="BB3" s="0">
-        <v>0.0044510705739636003</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="BC3" s="0">
-        <v>0.0051602857834619721</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="BD3" s="0">
-        <v>0.48272798853123233</v>
+        <v>0</v>
       </c>
       <c r="BE3" s="0">
-        <v>0.0054706650007571378</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="BF3" s="0">
-        <v>0.0050035139646711201</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="BG3" s="0">
-        <v>0.87095528327930316</v>
+        <v>0</v>
       </c>
       <c r="BH3" s="0">
-        <v>0.0055474252285685711</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="BI3" s="0">
-        <v>0.0057565482635376997</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="BJ3" s="0">
-        <v>1.1266305069590525</v>
+        <v>0</v>
       </c>
       <c r="BK3" s="0">
-        <v>0.0054835136114045058</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="BL3" s="0">
-        <v>0.0052189034798344747</v>
+        <v>0.0034897154942680124</v>
       </c>
       <c r="BM3" s="0">
-        <v>1.1509312389750903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -919,196 +919,196 @@
         <v>2</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.00061014563687977882</v>
+        <v>-2.2440612965339039e-08</v>
       </c>
       <c r="C4" s="0">
         <v>0</v>
       </c>
       <c r="D4" s="0">
-        <v>7.4718378519608093e-06</v>
+        <v>0.00011270048782022072</v>
       </c>
       <c r="E4" s="0">
-        <v>0.23266138437549172</v>
+        <v>2.6554258739854175e-05</v>
       </c>
       <c r="F4" s="0">
-        <v>0.004321478746906156</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="G4" s="0">
-        <v>0.0058277608999258981</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="H4" s="0">
         <v>0</v>
       </c>
       <c r="I4" s="0">
-        <v>0.0033932368139779723</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="J4" s="0">
-        <v>0.0047555577349968851</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="K4" s="0">
-        <v>0.42577978106065406</v>
+        <v>0</v>
       </c>
       <c r="L4" s="0">
-        <v>0.0048096438340624265</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="M4" s="0">
-        <v>0.004583382866543962</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="N4" s="0">
-        <v>0.43962054193594335</v>
+        <v>0</v>
       </c>
       <c r="O4" s="0">
-        <v>0.0043318041758134288</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="P4" s="0">
-        <v>0.001371118148905432</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.021057991294898049</v>
+        <v>0</v>
       </c>
       <c r="R4" s="0">
-        <v>0.0059111886709457048</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="S4" s="0">
-        <v>0.005614106205045555</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="T4" s="0">
-        <v>0.63397581027913885</v>
+        <v>0</v>
       </c>
       <c r="U4" s="0">
-        <v>0.0024501557702727942</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="V4" s="0">
-        <v>0.0054780969163113948</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="W4" s="0">
-        <v>0.38236104973439894</v>
+        <v>0</v>
       </c>
       <c r="X4" s="0">
-        <v>0.0040587201781303057</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.001444019773422566</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.21064924672671892</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.0017072718196780203</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.0020862117832350139</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AC4" s="0">
-        <v>0.3701394863707132</v>
+        <v>0</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.0017242219082763653</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AE4" s="0">
-        <v>0.0020959866275774733</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.10284909354133283</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="0">
-        <v>0.001240114632674998</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.0039074436091388869</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AI4" s="0">
-        <v>1.3651994596110364</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.0017228357260645779</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.0018632227994546571</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AL4" s="0">
-        <v>0.83667713626390527</v>
+        <v>0</v>
       </c>
       <c r="AM4" s="0">
-        <v>0.0017221122405967431</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AN4" s="0">
-        <v>0.0017668746651755228</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AO4" s="0">
-        <v>0.26512953181248955</v>
+        <v>0</v>
       </c>
       <c r="AP4" s="0">
-        <v>0.0024584988694045921</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AQ4" s="0">
-        <v>0.0013503244191921586</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AR4" s="0">
-        <v>0.37541500750635132</v>
+        <v>0</v>
       </c>
       <c r="AS4" s="0">
-        <v>0.0024937045093600466</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AT4" s="0">
-        <v>0.0012746773367357897</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AU4" s="0">
-        <v>0.98598473702972267</v>
+        <v>0</v>
       </c>
       <c r="AV4" s="0">
-        <v>0.002101512603996904</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AW4" s="0">
-        <v>0.0012714515482242462</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AX4" s="0">
-        <v>0.52290492230064822</v>
+        <v>0</v>
       </c>
       <c r="AY4" s="0">
-        <v>0.0031774708923572098</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="AZ4" s="0">
-        <v>0.0023929866024348817</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="BA4" s="0">
-        <v>0.158245175342902</v>
+        <v>0</v>
       </c>
       <c r="BB4" s="0">
-        <v>0.004451123669408771</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="BC4" s="0">
-        <v>0.005160518942521705</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="BD4" s="0">
-        <v>0.48272798796599836</v>
+        <v>0</v>
       </c>
       <c r="BE4" s="0">
-        <v>0.0054709478322056554</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="BF4" s="0">
-        <v>0.0050037528449982773</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="BG4" s="0">
-        <v>0.87095528345595885</v>
+        <v>0</v>
       </c>
       <c r="BH4" s="0">
-        <v>0.0055476721380201535</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="BI4" s="0">
-        <v>0.0057567866881181491</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="BJ4" s="0">
-        <v>1.1266305068845013</v>
+        <v>0</v>
       </c>
       <c r="BK4" s="0">
-        <v>0.0054835792463206086</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="BL4" s="0">
-        <v>0.0052191918996013593</v>
+        <v>0.0033770150064477917</v>
       </c>
       <c r="BM4" s="0">
-        <v>1.150931238958079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1116,196 +1116,196 @@
         <v>3</v>
       </c>
       <c r="B5" s="0">
-        <v>-0.00061054012490929159</v>
+        <v>-5.3780423791918659e-08</v>
       </c>
       <c r="C5" s="0">
         <v>0</v>
       </c>
       <c r="D5" s="0">
-        <v>2.5634067915188319e-06</v>
+        <v>0.00066385646849635542</v>
       </c>
       <c r="E5" s="0">
-        <v>0.2324752179646416</v>
+        <v>7.9013148123582665e-05</v>
       </c>
       <c r="F5" s="0">
-        <v>0.0043215176865520422</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="G5" s="0">
-        <v>0.005827780902436578</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="H5" s="0">
         <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>0.0033932602054036944</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="J5" s="0">
-        <v>0.0047555957669223343</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="K5" s="0">
-        <v>0.42577978126275517</v>
+        <v>0</v>
       </c>
       <c r="L5" s="0">
-        <v>0.00480983856910295</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="M5" s="0">
-        <v>0.0045836221871041758</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="N5" s="0">
-        <v>0.43962054179883936</v>
+        <v>0</v>
       </c>
       <c r="O5" s="0">
-        <v>0.0043322633596091457</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="P5" s="0">
-        <v>0.0013709730483504219</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.021057957463932391</v>
+        <v>0</v>
       </c>
       <c r="R5" s="0">
-        <v>0.0059112233945860741</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="S5" s="0">
-        <v>0.005614257082613758</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="T5" s="0">
-        <v>0.63397581053015895</v>
+        <v>0</v>
       </c>
       <c r="U5" s="0">
-        <v>0.0024515436958416521</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="V5" s="0">
-        <v>0.0054783009710775874</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="W5" s="0">
-        <v>0.38236106085304439</v>
+        <v>0</v>
       </c>
       <c r="X5" s="0">
-        <v>0.0040593116301251148</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.0014438461696369546</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.21064919872363658</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.0017069952890532557</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.0020857870938656826</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.37013949422061371</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.0017239387504702829</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AE5" s="0">
-        <v>0.0020963660986277137</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.10284911653776782</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.0012400207521505073</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.0039063068507168286</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AI5" s="0">
-        <v>1.3651993892402987</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="0">
-        <v>0.0017225531102309343</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.0018628852947875647</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AL5" s="0">
-        <v>0.83667713799504373</v>
+        <v>0</v>
       </c>
       <c r="AM5" s="0">
-        <v>0.0017218299076329705</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AN5" s="0">
-        <v>0.00176657483090477</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AO5" s="0">
-        <v>0.26512953368826797</v>
+        <v>0</v>
       </c>
       <c r="AP5" s="0">
-        <v>0.0024579286224466986</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AQ5" s="0">
-        <v>0.0013501874486133597</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AR5" s="0">
-        <v>0.37541501636873115</v>
+        <v>0</v>
       </c>
       <c r="AS5" s="0">
-        <v>0.0024931204976269407</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AT5" s="0">
-        <v>0.0012745699428125159</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AU5" s="0">
-        <v>0.98598478218375996</v>
+        <v>0</v>
       </c>
       <c r="AV5" s="0">
-        <v>0.0021010819322804654</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AW5" s="0">
-        <v>0.0012713454155265545</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AX5" s="0">
-        <v>0.52290495987972641</v>
+        <v>0</v>
       </c>
       <c r="AY5" s="0">
-        <v>0.0031766195402044483</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="AZ5" s="0">
-        <v>0.0023928766320346208</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="BA5" s="0">
-        <v>0.15824517816321695</v>
+        <v>0</v>
       </c>
       <c r="BB5" s="0">
-        <v>0.0044511926714771374</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="BC5" s="0">
-        <v>0.0051606269584552967</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="BD5" s="0">
-        <v>0.48272798829013291</v>
+        <v>0</v>
       </c>
       <c r="BE5" s="0">
-        <v>0.0054710969766803112</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="BF5" s="0">
-        <v>0.0050038139077852621</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="BG5" s="0">
-        <v>0.87095528379427034</v>
+        <v>0</v>
       </c>
       <c r="BH5" s="0">
-        <v>0.0055478310475901883</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="BI5" s="0">
-        <v>0.0057568525053968336</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="BJ5" s="0">
-        <v>1.1266305070202158</v>
+        <v>0</v>
       </c>
       <c r="BK5" s="0">
-        <v>0.0054835797109591099</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="BL5" s="0">
-        <v>0.0052192806324072799</v>
+        <v>0.0027131585379514362</v>
       </c>
       <c r="BM5" s="0">
-        <v>1.1509312389338517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1313,196 +1313,1181 @@
         <v>4</v>
       </c>
       <c r="B6" s="0">
-        <v>-0.00061054012490929159</v>
+        <v>-1.0550066580632055e-07</v>
       </c>
       <c r="C6" s="0">
         <v>0</v>
       </c>
       <c r="D6" s="0">
-        <v>1.9777560644359753e-06</v>
+        <v>0.00042290002286824628</v>
       </c>
       <c r="E6" s="0">
-        <v>0.011102829173432043</v>
+        <v>0.00011062999765955944</v>
       </c>
       <c r="F6" s="0">
-        <v>0.0043215176865520422</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="G6" s="0">
-        <v>0.005827780902436578</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="H6" s="0">
         <v>0</v>
       </c>
       <c r="I6" s="0">
-        <v>0.0033932602054036944</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="J6" s="0">
-        <v>0.0047555957669223343</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="K6" s="0">
-        <v>0.42577978126275517</v>
+        <v>0</v>
       </c>
       <c r="L6" s="0">
-        <v>0.00480983856910295</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="M6" s="0">
-        <v>0.0045836221871041758</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="N6" s="0">
-        <v>0.43962054179883936</v>
+        <v>0</v>
       </c>
       <c r="O6" s="0">
-        <v>0.0043322633596091457</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="P6" s="0">
-        <v>0.0013709730483504219</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.021057957463932391</v>
+        <v>0</v>
       </c>
       <c r="R6" s="0">
-        <v>0.0059112233945860741</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="S6" s="0">
-        <v>0.005614257082613758</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="T6" s="0">
-        <v>0.63397581053015895</v>
+        <v>0</v>
       </c>
       <c r="U6" s="0">
-        <v>0.0024515436958416521</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="V6" s="0">
-        <v>0.0054783009710775874</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="W6" s="0">
-        <v>0.38236106085304439</v>
+        <v>0</v>
       </c>
       <c r="X6" s="0">
-        <v>0.0040593116301251148</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.0014438461696369546</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="Z6" s="0">
-        <v>0.21064919872363658</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="0">
-        <v>0.0017069952890532557</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AB6" s="0">
-        <v>0.0020857870938656826</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AC6" s="0">
-        <v>0.37013949422061371</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="0">
-        <v>0.0017239387504702829</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AE6" s="0">
-        <v>0.0020963660986277137</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AF6" s="0">
-        <v>0.10284911653776782</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.0012400207521505073</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.0039063068507168286</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AI6" s="0">
-        <v>1.3651993892402987</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.0017225531102309343</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AK6" s="0">
-        <v>0.0018628852947875647</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AL6" s="0">
-        <v>0.83667713799504373</v>
+        <v>0</v>
       </c>
       <c r="AM6" s="0">
-        <v>0.0017218299076329705</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AN6" s="0">
-        <v>0.00176657483090477</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AO6" s="0">
-        <v>0.26512953368826797</v>
+        <v>0</v>
       </c>
       <c r="AP6" s="0">
-        <v>0.0024579286224466986</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AQ6" s="0">
-        <v>0.0013501874486133597</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AR6" s="0">
-        <v>0.37541501636873115</v>
+        <v>0</v>
       </c>
       <c r="AS6" s="0">
-        <v>0.0024931204976269407</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AT6" s="0">
-        <v>0.0012745699428125159</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AU6" s="0">
-        <v>0.98598478218375996</v>
+        <v>0</v>
       </c>
       <c r="AV6" s="0">
-        <v>0.0021010819322804654</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AW6" s="0">
-        <v>0.0012713454155265545</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AX6" s="0">
-        <v>0.52290495987972641</v>
+        <v>0</v>
       </c>
       <c r="AY6" s="0">
-        <v>0.0031766195402044483</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="AZ6" s="0">
-        <v>0.0023928766320346208</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="BA6" s="0">
-        <v>0.15824517816321695</v>
+        <v>0</v>
       </c>
       <c r="BB6" s="0">
-        <v>0.0044511926714771374</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="BC6" s="0">
-        <v>0.0051606269584552967</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="BD6" s="0">
-        <v>0.48272798829013291</v>
+        <v>0</v>
       </c>
       <c r="BE6" s="0">
-        <v>0.0054710969766803112</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="BF6" s="0">
-        <v>0.0050038139077852621</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="BG6" s="0">
-        <v>0.87095528379427034</v>
+        <v>0</v>
       </c>
       <c r="BH6" s="0">
-        <v>0.0055478310475901883</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="BI6" s="0">
-        <v>0.0057568525053968336</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="BJ6" s="0">
-        <v>1.1266305070202158</v>
+        <v>0</v>
       </c>
       <c r="BK6" s="0">
-        <v>0.0054835797109591099</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="BL6" s="0">
-        <v>0.0052192806324072799</v>
+        <v>0.00229025851508319</v>
       </c>
       <c r="BM6" s="0">
-        <v>1.1509312389338517</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>5</v>
+      </c>
+      <c r="B7" s="0">
+        <v>-1.432147833410114e-07</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0.00016876274167666174</v>
+      </c>
+      <c r="E7" s="0">
+        <v>0.00017471190559429544</v>
+      </c>
+      <c r="F7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="G7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="H7" s="0">
+        <v>0</v>
+      </c>
+      <c r="I7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="J7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="K7" s="0">
+        <v>0</v>
+      </c>
+      <c r="L7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="M7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="N7" s="0">
+        <v>0</v>
+      </c>
+      <c r="O7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="P7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="Q7" s="0">
+        <v>0</v>
+      </c>
+      <c r="R7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="S7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="T7" s="0">
+        <v>0</v>
+      </c>
+      <c r="U7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="V7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="W7" s="0">
+        <v>0</v>
+      </c>
+      <c r="X7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="Y7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="Z7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AC7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AE7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AF7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AH7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AI7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AK7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AL7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AN7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AO7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AQ7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AR7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AT7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AU7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AW7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AX7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="AZ7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="BA7" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="BC7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="BD7" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="BF7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="BG7" s="0">
+        <v>0</v>
+      </c>
+      <c r="BH7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="BI7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="BJ7" s="0">
+        <v>0</v>
+      </c>
+      <c r="BK7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="BL7" s="0">
+        <v>0.0021214957734065282</v>
+      </c>
+      <c r="BM7" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>6</v>
+      </c>
+      <c r="B8" s="0">
+        <v>-1.5813090870858582e-07</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0</v>
+      </c>
+      <c r="D8" s="0">
+        <v>5.2004414691094288e-05</v>
+      </c>
+      <c r="E8" s="0">
+        <v>0.00018875408451109822</v>
+      </c>
+      <c r="F8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="H8" s="0">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="M8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="N8" s="0">
+        <v>0</v>
+      </c>
+      <c r="O8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="P8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="Q8" s="0">
+        <v>0</v>
+      </c>
+      <c r="R8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="S8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="T8" s="0">
+        <v>0</v>
+      </c>
+      <c r="U8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="V8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="W8" s="0">
+        <v>0</v>
+      </c>
+      <c r="X8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="Y8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="Z8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AE8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AF8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AH8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AI8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AK8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AL8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AN8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AO8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AQ8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AR8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AT8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AU8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AW8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AX8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="AZ8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="BA8" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="BC8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="BD8" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="BF8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="BG8" s="0">
+        <v>0</v>
+      </c>
+      <c r="BH8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="BI8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="BJ8" s="0">
+        <v>0</v>
+      </c>
+      <c r="BK8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="BL8" s="0">
+        <v>0.0020696324387377489</v>
+      </c>
+      <c r="BM8" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>7</v>
+      </c>
+      <c r="B9" s="0">
+        <v>-1.6454825937002823e-07</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0</v>
+      </c>
+      <c r="D9" s="0">
+        <v>2.0386514307258082e-05</v>
+      </c>
+      <c r="E9" s="0">
+        <v>8.2990879911384755e-06</v>
+      </c>
+      <c r="F9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="G9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="H9" s="0">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="J9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="K9" s="0">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="M9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="N9" s="0">
+        <v>0</v>
+      </c>
+      <c r="O9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="P9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="Q9" s="0">
+        <v>0</v>
+      </c>
+      <c r="R9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="S9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="T9" s="0">
+        <v>0</v>
+      </c>
+      <c r="U9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="V9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="W9" s="0">
+        <v>0</v>
+      </c>
+      <c r="X9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="Y9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="Z9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AE9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AF9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AH9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AI9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AK9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AL9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AN9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AO9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AQ9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AR9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AT9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AU9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AW9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AX9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="AZ9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="BA9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="BC9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="BD9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="BF9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="BG9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BH9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="BI9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="BJ9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BK9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="BL9" s="0">
+        <v>0.0020492459244304908</v>
+      </c>
+      <c r="BM9" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>8</v>
+      </c>
+      <c r="B10" s="0">
+        <v>-1.6506070340467865e-07</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0</v>
+      </c>
+      <c r="D10" s="0">
+        <v>1.6925257367581339e-06</v>
+      </c>
+      <c r="E10" s="0">
+        <v>0.00010351230734885483</v>
+      </c>
+      <c r="F10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="G10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="H10" s="0">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="J10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="K10" s="0">
+        <v>0</v>
+      </c>
+      <c r="L10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="M10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="N10" s="0">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="P10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="Q10" s="0">
+        <v>0</v>
+      </c>
+      <c r="R10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="S10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="T10" s="0">
+        <v>0</v>
+      </c>
+      <c r="U10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="V10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="W10" s="0">
+        <v>0</v>
+      </c>
+      <c r="X10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="Y10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="Z10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AE10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AF10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AH10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AI10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AK10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AL10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AN10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AO10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AQ10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AR10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AT10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AU10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AW10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AX10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="AZ10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="BA10" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="BC10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="BD10" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="BF10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="BG10" s="0">
+        <v>0</v>
+      </c>
+      <c r="BH10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="BI10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="BJ10" s="0">
+        <v>0</v>
+      </c>
+      <c r="BK10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="BL10" s="0">
+        <v>0.0020475533986937327</v>
+      </c>
+      <c r="BM10" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>9</v>
+      </c>
+      <c r="B11" s="0">
+        <v>-1.6506545677670461e-07</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1.4659352751220794e-08</v>
+      </c>
+      <c r="E11" s="0">
+        <v>4.2184644569989588e-15</v>
+      </c>
+      <c r="F11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="H11" s="0">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="J11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="K11" s="0">
+        <v>0</v>
+      </c>
+      <c r="L11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="N11" s="0">
+        <v>0</v>
+      </c>
+      <c r="O11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="P11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="Q11" s="0">
+        <v>0</v>
+      </c>
+      <c r="R11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="S11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="T11" s="0">
+        <v>0</v>
+      </c>
+      <c r="U11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="V11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="W11" s="0">
+        <v>0</v>
+      </c>
+      <c r="X11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="Y11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="Z11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AB11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AC11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AE11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AF11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AH11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AI11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AK11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AL11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AN11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AO11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AQ11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AR11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AT11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AU11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AW11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AX11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="AZ11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="BA11" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="BC11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="BD11" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="BF11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="BG11" s="0">
+        <v>0</v>
+      </c>
+      <c r="BH11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="BI11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="BJ11" s="0">
+        <v>0</v>
+      </c>
+      <c r="BK11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="BL11" s="0">
+        <v>0.0020475387393409815</v>
+      </c>
+      <c r="BM11" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
